--- a/src/data/output/cp_gl_ceb_output.xlsx
+++ b/src/data/output/cp_gl_ceb_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mudita\Documents\spg-automation\src\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23A5EC4-4F1E-44A3-96F4-5C488884E897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9BDF93-2F71-4BD9-9220-5B398E0AD175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1248" yWindow="840" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Output" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="174">
   <si>
     <t>Test ID</t>
   </si>
@@ -106,15 +106,72 @@
     <t>TS-005</t>
   </si>
   <si>
+    <t>0099962</t>
+  </si>
+  <si>
+    <t>244102.39</t>
+  </si>
+  <si>
+    <t>525.00</t>
+  </si>
+  <si>
+    <t>7323.07</t>
+  </si>
+  <si>
+    <t>251950.46</t>
+  </si>
+  <si>
     <t>TS-006</t>
   </si>
   <si>
+    <t>0099960</t>
+  </si>
+  <si>
+    <t>144852.65</t>
+  </si>
+  <si>
+    <t>4361.33</t>
+  </si>
+  <si>
+    <t>149738.98</t>
+  </si>
+  <si>
     <t>TS-007</t>
   </si>
   <si>
+    <t>0099961</t>
+  </si>
+  <si>
+    <t>84668.78</t>
+  </si>
+  <si>
+    <t>575.00</t>
+  </si>
+  <si>
+    <t>1917.99</t>
+  </si>
+  <si>
+    <t>87191.55</t>
+  </si>
+  <si>
     <t>TS-008</t>
   </si>
   <si>
+    <t>0099963</t>
+  </si>
+  <si>
+    <t>112321.15</t>
+  </si>
+  <si>
+    <t>425.00</t>
+  </si>
+  <si>
+    <t>3369.63</t>
+  </si>
+  <si>
+    <t>116115.78</t>
+  </si>
+  <si>
     <t>TS-009</t>
   </si>
   <si>
@@ -136,6 +193,18 @@
     <t>TS-010</t>
   </si>
   <si>
+    <t>0099964</t>
+  </si>
+  <si>
+    <t>62235.83</t>
+  </si>
+  <si>
+    <t>1878.32</t>
+  </si>
+  <si>
+    <t>64489.15</t>
+  </si>
+  <si>
     <t>TS-011</t>
   </si>
   <si>
@@ -157,16 +226,55 @@
     <t>TS-012</t>
   </si>
   <si>
+    <t>0099922</t>
+  </si>
+  <si>
+    <t>169787.26</t>
+  </si>
+  <si>
+    <t>5109.37</t>
+  </si>
+  <si>
+    <t>175421.63</t>
+  </si>
+  <si>
     <t>TS-013</t>
   </si>
   <si>
+    <t>0099919</t>
+  </si>
+  <si>
+    <t>124245.34</t>
+  </si>
+  <si>
+    <t>3727.36</t>
+  </si>
+  <si>
+    <t>128447.70</t>
+  </si>
+  <si>
     <t>TS-014</t>
   </si>
   <si>
+    <t>0099920</t>
+  </si>
+  <si>
+    <t>65099.84</t>
+  </si>
+  <si>
+    <t>295.00</t>
+  </si>
+  <si>
+    <t>1953.00</t>
+  </si>
+  <si>
+    <t>67347.84</t>
+  </si>
+  <si>
     <t>TS-015</t>
   </si>
   <si>
-    <t>0099856</t>
+    <t>0099921</t>
   </si>
   <si>
     <t>84516.04</t>
@@ -235,6 +343,21 @@
     <t>TS-020</t>
   </si>
   <si>
+    <t>0099968</t>
+  </si>
+  <si>
+    <t>73778.39</t>
+  </si>
+  <si>
+    <t>596.34</t>
+  </si>
+  <si>
+    <t>3688.92</t>
+  </si>
+  <si>
+    <t>78063.65</t>
+  </si>
+  <si>
     <t>TS-021</t>
   </si>
   <si>
@@ -244,9 +367,6 @@
     <t>128833.58</t>
   </si>
   <si>
-    <t>525.00</t>
-  </si>
-  <si>
     <t>5885.82</t>
   </si>
   <si>
@@ -274,6 +394,18 @@
     <t>TS-024</t>
   </si>
   <si>
+    <t>0099965</t>
+  </si>
+  <si>
+    <t>102539.57</t>
+  </si>
+  <si>
+    <t>3090.44</t>
+  </si>
+  <si>
+    <t>106105.01</t>
+  </si>
+  <si>
     <t>TS-025</t>
   </si>
   <si>
@@ -313,10 +445,49 @@
     <t>TS-028</t>
   </si>
   <si>
+    <t>0099967</t>
+  </si>
+  <si>
+    <t>81391.94</t>
+  </si>
+  <si>
+    <t>2451.51</t>
+  </si>
+  <si>
+    <t>84168.45</t>
+  </si>
+  <si>
     <t>TS-029</t>
   </si>
   <si>
+    <t>0099925</t>
+  </si>
+  <si>
+    <t>104651.78</t>
+  </si>
+  <si>
+    <t>738.96</t>
+  </si>
+  <si>
+    <t>5232.59</t>
+  </si>
+  <si>
+    <t>110623.33</t>
+  </si>
+  <si>
     <t>TS-030</t>
+  </si>
+  <si>
+    <t>0099924</t>
+  </si>
+  <si>
+    <t>710314.87</t>
+  </si>
+  <si>
+    <t>32343.21</t>
+  </si>
+  <si>
+    <t>743183.08</t>
   </si>
   <si>
     <t>TS-031</t>
@@ -406,12 +577,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -443,18 +620,20 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -799,1220 +978,1350 @@
   <dimension ref="A1:I121"/>
   <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="18.600000000000001" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="11.77734375" style="2"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.600000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>49442.9</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18.600000000000001" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18.600000000000001" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18.600000000000001" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18.600000000000001" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="A14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="A15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="A16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>51</v>
+      <c r="E16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>57</v>
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>63</v>
+      <c r="A18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="A19" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="A20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>69</v>
+      <c r="E20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="A21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>76</v>
+      <c r="A22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="A23" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="A24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>82</v>
+      <c r="E24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="A25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>89</v>
+      <c r="A26" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="A27" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18.600000000000001" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:6" ht="18.600000000000001" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="E29" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18.600000000000001" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="18.600000000000001" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18.600000000000001" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>103</v>
+      <c r="E32" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>109</v>
+      <c r="A33" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>115</v>
+      <c r="A34" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="A35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
     </row>
     <row r="36" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="A36" s="5"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+      <c r="A37" s="5"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="A38" s="5"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+      <c r="A39" s="5"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A42" s="6"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+      <c r="A42" s="5"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="A43" s="5"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A44" s="6"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
+      <c r="A44" s="5"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
+      <c r="A46" s="5"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
     </row>
     <row r="47" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
+      <c r="A47" s="5"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
+      <c r="A48" s="5"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
+      <c r="A49" s="5"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
+      <c r="A50" s="5"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A51" s="6"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
+      <c r="A51" s="5"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
+      <c r="A52" s="5"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
     </row>
     <row r="53" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+      <c r="A53" s="5"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
     </row>
     <row r="54" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
+      <c r="A54" s="5"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A55" s="6"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
+      <c r="A55" s="5"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A56" s="6"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
+      <c r="A56" s="5"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
     </row>
     <row r="57" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A57" s="6"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
+      <c r="A57" s="5"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
     </row>
     <row r="58" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A58" s="6"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+      <c r="A58" s="5"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
     </row>
     <row r="59" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A59" s="6"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
+      <c r="A59" s="5"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
     </row>
     <row r="60" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
+      <c r="A60" s="5"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
     </row>
     <row r="61" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A61" s="6"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
+      <c r="A61" s="5"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
     </row>
     <row r="62" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A62" s="6"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
+      <c r="A62" s="5"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
     </row>
     <row r="63" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A63" s="6"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
+      <c r="A63" s="5"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
     </row>
     <row r="64" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A64" s="6"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
+      <c r="A64" s="5"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
     </row>
     <row r="65" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
+      <c r="A65" s="5"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
     </row>
     <row r="66" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A66" s="6"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
+      <c r="A66" s="5"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
     </row>
     <row r="67" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A67" s="6"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
+      <c r="A67" s="5"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
     </row>
     <row r="68" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A68" s="6"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
+      <c r="A68" s="5"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
     </row>
     <row r="69" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A69" s="6"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
+      <c r="A69" s="5"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
     </row>
     <row r="70" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A70" s="6"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
+      <c r="A70" s="5"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
     </row>
     <row r="71" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A71" s="6"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
+      <c r="A71" s="5"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
     </row>
     <row r="72" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A72" s="6"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
+      <c r="A72" s="5"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
     </row>
     <row r="73" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A73" s="6"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
+      <c r="A73" s="5"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
     </row>
     <row r="74" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A74" s="6"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
+      <c r="A74" s="5"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
     </row>
     <row r="75" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A75" s="6"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
     </row>
     <row r="76" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A76" s="6"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
+      <c r="A76" s="5"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
     </row>
     <row r="77" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A77" s="6"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
     </row>
     <row r="78" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A78" s="6"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
+      <c r="A78" s="5"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A79" s="6"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
+      <c r="A79" s="5"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
     </row>
     <row r="80" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A80" s="6"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
+      <c r="A80" s="5"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
     </row>
     <row r="81" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
+      <c r="A81" s="5"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
+      <c r="A82" s="5"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
     </row>
     <row r="83" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A83" s="6"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
+      <c r="A83" s="5"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
     </row>
     <row r="84" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A84" s="6"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
+      <c r="A84" s="5"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
     </row>
     <row r="85" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
+      <c r="A85" s="5"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
     </row>
     <row r="86" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
+      <c r="A86" s="5"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
     </row>
     <row r="87" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A87" s="6"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
+      <c r="A87" s="5"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
     </row>
     <row r="88" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
+      <c r="A88" s="5"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
     </row>
     <row r="89" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A89" s="6"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
+      <c r="A89" s="5"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
     </row>
     <row r="90" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A90" s="6"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
+      <c r="A90" s="5"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
     </row>
     <row r="91" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A91" s="6"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
+      <c r="A91" s="5"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
     </row>
     <row r="92" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A92" s="6"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
+      <c r="A92" s="5"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
+      <c r="A93" s="5"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
     </row>
     <row r="94" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
+      <c r="A94" s="5"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
     </row>
     <row r="95" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
+      <c r="A95" s="5"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
     </row>
     <row r="96" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A96" s="6"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
+      <c r="A96" s="5"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
     </row>
     <row r="97" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
+      <c r="A97" s="5"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
     </row>
     <row r="98" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A98" s="6"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
+      <c r="A98" s="5"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
     </row>
     <row r="99" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A99" s="6"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
+      <c r="A99" s="5"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="100" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
+      <c r="A100" s="5"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
     </row>
     <row r="101" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
+      <c r="A101" s="5"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A102" s="6"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
+      <c r="A102" s="5"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
     </row>
     <row r="103" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A103" s="6"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
+      <c r="A103" s="5"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
     </row>
     <row r="104" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
+      <c r="A104" s="5"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
     </row>
     <row r="105" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A105" s="6"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
+      <c r="A105" s="5"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
     </row>
     <row r="106" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A106" s="6"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
+      <c r="A106" s="5"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
     </row>
     <row r="107" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A107" s="6"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
+      <c r="A107" s="5"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
     </row>
     <row r="108" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A108" s="6"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
+      <c r="A108" s="5"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
     </row>
     <row r="109" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A109" s="6"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-      <c r="E109" s="4"/>
-      <c r="F109" s="4"/>
+      <c r="A109" s="5"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
     </row>
     <row r="110" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A110" s="6"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
+      <c r="A110" s="5"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
     </row>
     <row r="111" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A111" s="6"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
-      <c r="F111" s="4"/>
+      <c r="A111" s="5"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
     </row>
     <row r="112" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A112" s="6"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
+      <c r="A112" s="5"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
     </row>
     <row r="113" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A113" s="6"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
+      <c r="A113" s="5"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
     </row>
     <row r="114" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A114" s="6"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-      <c r="F114" s="4"/>
+      <c r="A114" s="5"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
     </row>
     <row r="115" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A115" s="6"/>
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
-      <c r="E115" s="4"/>
-      <c r="F115" s="4"/>
+      <c r="A115" s="5"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
     </row>
     <row r="116" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A116" s="6"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
+      <c r="A116" s="5"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
     </row>
     <row r="117" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A117" s="6"/>
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
-      <c r="F117" s="4"/>
+      <c r="A117" s="5"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
     </row>
     <row r="118" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A118" s="6"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
-      <c r="F118" s="4"/>
+      <c r="A118" s="5"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
     </row>
     <row r="119" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A119" s="6"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
-      <c r="F119" s="4"/>
+      <c r="A119" s="5"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
     </row>
     <row r="120" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="4"/>
-      <c r="F120" s="4"/>
+      <c r="A120" s="5"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
     </row>
     <row r="121" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A121" s="6"/>
+      <c r="A121" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
